--- a/Luban/Config/Datas/Levels/L08/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L08/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L8 W1/25; N=38; EHP=220.704000; normal:17x19,normal:18x19</t>
+          <t>L8 W1/25; N=38; EHP=448.959755; normal:17x19,normal:18x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L8 W2/25; N=44; EHP=267.588499; normal:17x22,normal:18x22</t>
+          <t>L8 W2/25; N=44; EHP=544.332985; normal:17x22,normal:18x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3384136,3384673,3384019,3384136,3384673,3384091,3384136,3384673,3384099,3384136,3384673,3384099,3384136,3384673,3384107,3384136,3384673,3384115,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144</t>
+          <t>3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384673,3384136,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384144,3384136,3384136,3384136,3384136,3384136,3384136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L8 W3/25; N=50; EHP=336.399360; air:2x1,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x15,normal:18x15,swarm:84x14</t>
+          <t>L8 W3/25; N=50; EHP=738.333594; normal:17x21,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3386136,3386673,3386019,3386136,3386673,3386019,3386136,3386673,3386091,3386136,3386673,3386099,3386136,3386673,3386107,3386136,3386673,3386107,3386136,3386673,3386115,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386136,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144</t>
+          <t>3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386673,3386136,3386136,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386144,3386136,3386136,3386136,3386136,3386136,3386136,3386136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L8 W4/25; N=56; EHP=433.848307; air:2x2,air:11x1,air:12x1,air:13x2,air:14x1,normal:17x17,normal:18x17,swarm:84x15</t>
+          <t>L8 W4/25; N=56; EHP=954.988890; normal:17x24,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3388136,3388673,3388019,3388668,3388136,3388673,3388091,3388668,3388136,3388673,3388091,3388668,3388136,3388673,3388099,3388868,3388136,3388673,3388107,3388868,3388136,3388673,3388107,3388868,3388136,3388673,3388115,3388988,3388136,3388673,3388988,3388136,3388673,3388988,3388136,3388673,3388136,3388673,3388136,3388673,3388136,3388673,3388136,3388673,3388136,3388673,3388144,3388673,3388144,3388673,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144</t>
+          <t>3388136,3388019,3388019,3388668,3388136,3388091,3388091,3388668,3388136,3388091,3388091,3388668,3388136,3388099,3388099,3388868,3388136,3388107,3388107,3388868,3388136,3388107,3388107,3388868,3388136,3388115,3388115,3388988,3388136,3388673,3388988,3388136,3388673,3388988,3388136,3388673,3388136,3388673,3388136,3388673,3388136,3388673,3388136,3388673,3388136,3388673,3388144,3388673,3388144,3388673,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144,3388144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L8 W5/25; N=62; EHP=827.304716; air:2x1,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x15,normal:18x14,medium:83x3,swarm:84x17,medium:108x3,medium:123x3</t>
+          <t>L8 W5/25; N=62; EHP=1703.054510; air:2x2,air:11x4,air:12x2,air:13x4,air:14x2,medium:83x3,medium:108x3,medium:123x3,normal:17x15,normal:18x14,swarm:84x10 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3390136,3390673,3390242,3390019,3390668,3390136,3390673,3390242,3390091,3390668,3390136,3390673,3390242,3390091,3390668,3390136,3390673,3390466,3390099,3390868,3390136,3390673,3390466,3390099,3390868,3390136,3390673,3390466,3390107,3390868,3390136,3390673,3390786,3390115,3390868,3390136,3390673,3390786,3390115,3390988,3390136,3390673,3390988,3390136,3390673,3390988,3390136,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390144,3390144,3390144</t>
+          <t>3390136,3390019,3390242,3390019,3390668,3390136,3390091,3390242,3390091,3390668,3390136,3390091,3390242,3390091,3390668,3390136,3390099,3390466,3390099,3390868,3390136,3390099,3390466,3390099,3390868,3390136,3390107,3390466,3390107,3390868,3390136,3390115,3390786,3390115,3390868,3390136,3390115,3390786,3390115,3390988,3390136,3390673,3390988,3390136,3390673,3390988,3390136,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390673,3390144,3390144,3390144,3390144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L8 W6/25; N=68; EHP=844.000000; air:2x1,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x11,normal:18x12,fast:30x3,fast:58x3,medium:83x3,swarm:84x19,fast:98x2,medium:108x4,medium:123x3</t>
+          <t>L8 W6/25; N=68; EHP=1738.767362; air:2x2,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x3,fast:58x3,fast:98x2,medium:83x3,medium:108x4,medium:123x3,normal:17x11,normal:18x12,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3392136,3392673,3392242,3392019,3392668,3392136,3392673,3392242,3392019,3392668,3392136,3392673,3392242,3392091,3392668,3392136,3392673,3392466,3392099,3392668,3392136,3392673,3392466,3392099,3392868,3392136,3392673,3392786,3392107,3392868,3392136,3392673,3392786,3392107,3392868,3392136,3392673,3392786,3392115,3392988,3392136,3392673,3392115,3392988,3392136,3392673,3392988,3392136,3392673,3392988,3392136,3392673,3392136,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392144,3392144,3392144,3392144,3392144</t>
+          <t>3392136,3392019,3392242,3392019,3392668,3392136,3392019,3392242,3392019,3392668,3392136,3392091,3392242,3392091,3392668,3392136,3392099,3392466,3392099,3392668,3392136,3392099,3392466,3392099,3392868,3392136,3392107,3392786,3392107,3392868,3392136,3392107,3392786,3392107,3392868,3392136,3392115,3392786,3392115,3392988,3392136,3392115,3392115,3392988,3392136,3392673,3392988,3392136,3392673,3392988,3392136,3392673,3392136,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392673,3392144,3392144,3392144,3392144,3392144,3392144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L8 W7/25; N=74; EHP=965.140915; air:2x2,air:11x1,air:12x2,air:13x2,air:14x2,normal:17x13,normal:18x13,fast:30x3,fast:58x2,medium:83x4,swarm:84x20,fast:98x3,medium:108x3,medium:123x4</t>
+          <t>L8 W7/25; N=74; EHP=1989.082178; air:2x4,air:11x2,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:98x3,medium:83x4,medium:108x3,medium:123x4,normal:17x13,normal:18x13,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3394136,3394673,3394242,3394019,3394668,3394136,3394673,3394242,3394019,3394668,3394136,3394673,3394242,3394091,3394668,3394136,3394673,3394466,3394091,3394668,3394136,3394673,3394466,3394099,3394868,3394136,3394673,3394466,3394099,3394868,3394136,3394673,3394786,3394107,3394868,3394136,3394673,3394786,3394107,3394868,3394136,3394673,3394786,3394115,3394988,3394136,3394673,3394115,3394988,3394136,3394673,3394988,3394136,3394673,3394988,3394136,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394144,3394144,3394144,3394144</t>
+          <t>3394136,3394019,3394242,3394019,3394668,3394136,3394019,3394242,3394019,3394668,3394136,3394091,3394242,3394091,3394668,3394136,3394091,3394466,3394091,3394668,3394136,3394099,3394466,3394099,3394868,3394136,3394099,3394466,3394099,3394868,3394136,3394107,3394786,3394107,3394868,3394136,3394107,3394786,3394107,3394868,3394136,3394115,3394786,3394115,3394988,3394136,3394115,3394115,3394988,3394136,3394673,3394988,3394136,3394673,3394988,3394136,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394673,3394144,3394144,3394144,3394144,3394144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L8 W8/25; N=80; EHP=1244.259456; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x13,normal:18x14,fast:30x3,fast:58x3,medium:83x4,swarm:84x22,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L8 W8/25; N=80; EHP=2565.366760; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x13,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3396136,3396673,3396242,3396019,3396668,3396136,3396673,3396242,3396019,3396668,3396136,3396673,3396242,3396091,3396668,3396136,3396673,3396466,3396091,3396668,3396136,3396673,3396466,3396099,3396868,3396136,3396673,3396466,3396099,3396868,3396136,3396673,3396466,3396107,3396868,3396136,3396673,3396786,3396107,3396868,3396136,3396673,3396786,3396115,3396988,3396136,3396673,3396786,3396115,3396988,3396136,3396673,3396988,3396136,3396673,3396988,3396136,3396673,3396136,3396673,3396136,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396144,3396144,3396144,3396144,3396144</t>
+          <t>3396136,3396019,3396242,3396019,3396668,3396136,3396019,3396242,3396019,3396668,3396136,3396091,3396242,3396091,3396668,3396136,3396091,3396466,3396091,3396668,3396136,3396099,3396466,3396099,3396868,3396136,3396099,3396466,3396099,3396868,3396136,3396107,3396466,3396107,3396868,3396136,3396107,3396786,3396107,3396868,3396136,3396115,3396786,3396115,3396988,3396136,3396115,3396786,3396115,3396988,3396136,3396673,3396988,3396136,3396673,3396988,3396136,3396673,3396136,3396673,3396136,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396673,3396144,3396144,3396144,3396144,3396144,3396144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L8 W9/25; N=86; EHP=1589.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x3,fast:58x4,medium:83x4,swarm:84x24,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L8 W9/25; N=86; EHP=3273.286362; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x4,fast:98x3,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3398136,3398673,3398242,3398019,3398668,3398136,3398673,3398242,3398019,3398668,3398136,3398673,3398242,3398091,3398668,3398136,3398673,3398242,3398091,3398668,3398136,3398673,3398466,3398099,3398668,3398136,3398673,3398466,3398099,3398868,3398136,3398673,3398466,3398107,3398868,3398136,3398673,3398786,3398107,3398868,3398136,3398673,3398786,3398107,3398868,3398136,3398673,3398786,3398115,3398988,3398136,3398673,3398786,3398115,3398988,3398136,3398673,3398988,3398136,3398673,3398988,3398136,3398673,3398136,3398673,3398136,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398144,3398144,3398144,3398144,3398144,3398144</t>
+          <t>3398136,3398019,3398242,3398019,3398668,3398136,3398019,3398242,3398019,3398668,3398136,3398091,3398242,3398091,3398668,3398136,3398091,3398242,3398091,3398668,3398136,3398099,3398466,3398099,3398668,3398136,3398099,3398466,3398099,3398868,3398136,3398107,3398466,3398107,3398868,3398136,3398107,3398786,3398107,3398868,3398136,3398107,3398786,3398107,3398868,3398136,3398115,3398786,3398115,3398988,3398136,3398115,3398786,3398115,3398988,3398136,3398673,3398988,3398136,3398673,3398988,3398136,3398673,3398136,3398673,3398136,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398673,3398144,3398144,3398144,3398144,3398144,3398144,3398144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L8 W10/25; N=92; EHP=2934.000000; air:2x2,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x16,normal:18x16,fast:30x4,fast:58x3,medium:83x5,swarm:84x25,fast:98x4,medium:108x4,medium:123x4</t>
+          <t>L8 W10/25; N=92; EHP=6045.949063; air:2x4,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x4,fast:58x3,fast:98x4,medium:83x5,medium:108x4,medium:123x4,normal:17x16,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3400136,3400673,3400242,3400019,3400668,3400253,3400136,3400673,3400242,3400019,3400668,3400253,3400136,3400673,3400242,3400091,3400668,3400325,3400136,3400673,3400466,3400091,3400668,3400645,3400136,3400673,3400466,3400091,3400868,3400645,3400136,3400673,3400466,3400099,3400868,3400693,3400136,3400673,3400466,3400099,3400868,3400693,3400136,3400673,3400786,3400107,3400868,3400709,3400136,3400673,3400786,3400107,3400868,3401021,3400136,3400673,3400786,3400115,3400988,3400136,3400673,3400786,3400115,3400988,3400136,3400673,3400115,3400988,3400136,3400673,3400988,3400144,3400673,3400988,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400673,3400673</t>
+          <t>3400136,3400019,3400242,3400019,3400668,3400253,3400136,3400019,3400242,3400019,3400668,3400253,3400136,3400091,3400242,3400091,3400668,3400325,3400136,3400091,3400466,3400091,3400668,3400645,3400136,3400091,3400466,3400091,3400868,3400645,3400136,3400099,3400466,3400099,3400868,3400693,3400136,3400099,3400466,3400099,3400868,3400693,3400136,3400107,3400786,3400107,3400868,3400709,3400136,3400107,3400786,3400107,3400868,3401021,3400136,3400115,3400786,3400115,3400988,3400136,3400115,3400786,3400115,3400988,3400136,3400115,3400115,3400988,3400136,3400673,3400988,3400144,3400673,3400988,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400144,3400673,3400673,3400673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L8 W11/25; N=98; EHP=2993.000000; air:2x2,air:11x3,air:12x2,air:13x2,air:14x3,normal:17x13,normal:18x12,fast:30x3,heavy:31x2,heavy:40x1,fast:58x4,heavy:80x2,medium:83x4,swarm:84x27,heavy:86x2,heavy:88x1,fast:98x4,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L8 W11/25; N=98; EHP=6160.819725; air:2x4,air:11x6,air:12x4,air:13x4,air:14x6,fast:30x3,fast:58x4,fast:98x4,heavy:31x2,heavy:40x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x4,medium:108x5,medium:123x5,normal:17x13,normal:18x12,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3402136,3402673,3402242,3402019,3402668,3402253,3402136,3402673,3402242,3402019,3402668,3402253,3402136,3402673,3402242,3402091,3402668,3402325,3402136,3402673,3402242,3402091,3402668,3402325,3402136,3402673,3402466,3402099,3402668,3402645,3402136,3402673,3402466,3402099,3402868,3402693,3402136,3402673,3402466,3402099,3402868,3402693,3402136,3402673,3402466,3402107,3402868,3402709,3402136,3402673,3402786,3402107,3402868,3403021,3402136,3402673,3402786,3402115,3402868,3403021,3402136,3402673,3402786,3402115,3402988,3402136,3402673,3402786,3402115,3402988,3402136,3402673,3402988,3402144,3402673,3402988,3402144,3402673,3402988,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402673,3402673,3402673</t>
+          <t>3402136,3402019,3402242,3402019,3402668,3402253,3402136,3402019,3402242,3402019,3402668,3402253,3402136,3402091,3402242,3402091,3402668,3402325,3402136,3402091,3402242,3402091,3402668,3402325,3402136,3402099,3402466,3402099,3402668,3402645,3402136,3402099,3402466,3402099,3402868,3402693,3402136,3402099,3402466,3402099,3402868,3402693,3402136,3402107,3402466,3402107,3402868,3402709,3402136,3402107,3402786,3402107,3402868,3403021,3402136,3402115,3402786,3402115,3402868,3403021,3402136,3402115,3402786,3402115,3402988,3402136,3402115,3402786,3402115,3402988,3402136,3402673,3402988,3402144,3402673,3402988,3402144,3402673,3402988,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402144,3402673,3402673,3402673,3402673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L8 W12/25; N=104; EHP=3098.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x13,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,heavy:80x1,medium:83x5,swarm:84x29,heavy:86x2,heavy:88x1,fast:98x4,medium:108x5,medium:123x5,heavy:127x2</t>
+          <t>L8 W12/25; N=104; EHP=6372.057923; air:2x4,air:11x4,air:12x6,air:13x4,air:14x6,fast:30x4,fast:58x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x5,medium:108x5,medium:123x5,normal:17x13,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3404136,3404673,3404242,3404019,3404668,3404253,3404136,3404673,3404242,3404019,3404668,3404253,3404136,3404673,3404242,3404019,3404668,3404325,3404136,3404673,3404242,3404091,3404668,3404325,3404136,3404673,3404242,3404091,3404668,3404645,3404136,3404673,3404466,3404099,3404668,3404645,3404136,3404673,3404466,3404099,3404868,3404693,3404136,3404673,3404466,3404099,3404868,3404709,3404136,3404673,3404466,3404107,3404868,3404709,3404136,3404673,3404786,3404107,3404868,3405021,3404136,3404673,3404786,3404107,3404868,3405021,3404136,3404673,3404786,3404115,3404988,3404136,3404673,3404786,3404115,3404988,3404136,3404673,3404988,3404144,3404673,3404988,3404144,3404673,3404988,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404673,3404673,3404673</t>
+          <t>3404136,3404019,3404242,3404019,3404668,3404253,3404136,3404019,3404242,3404019,3404668,3404253,3404136,3404019,3404242,3404019,3404668,3404325,3404136,3404091,3404242,3404091,3404668,3404325,3404136,3404091,3404242,3404091,3404668,3404645,3404136,3404099,3404466,3404099,3404668,3404645,3404136,3404099,3404466,3404099,3404868,3404693,3404136,3404099,3404466,3404099,3404868,3404709,3404136,3404107,3404466,3404107,3404868,3404709,3404136,3404107,3404786,3404107,3404868,3405021,3404136,3404107,3404786,3404107,3404868,3405021,3404136,3404115,3404786,3404115,3404988,3404136,3404115,3404786,3404115,3404988,3404136,3404673,3404988,3404144,3404673,3404988,3404144,3404673,3404988,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404144,3404673,3404673,3404673,3404673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L8 W13/25; N=110; EHP=3780.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x2,normal:17x14,normal:18x13,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,heavy:80x2,medium:83x6,swarm:84x30,heavy:86x1,heavy:88x2,fast:98x4,medium:108x5,medium:123x5,heavy:127x2</t>
+          <t>L8 W13/25; N=110; EHP=7776.413395; air:2x6,air:11x4,air:12x6,air:13x6,air:14x4,fast:30x5,fast:58x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x6,medium:108x5,medium:123x5,normal:17x14,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3406136,3406673,3406242,3406019,3406668,3406253,3406136,3406673,3406242,3406019,3406668,3406325,3406136,3406673,3406242,3406019,3406668,3406325,3406136,3406673,3406242,3406091,3406668,3406645,3406136,3406673,3406466,3406091,3406668,3406645,3406136,3406673,3406466,3406091,3406868,3406693,3406136,3406673,3406466,3406099,3406868,3406693,3406136,3406673,3406466,3406099,3406868,3406709,3406136,3406673,3406786,3406107,3406868,3406709,3406136,3406673,3406786,3406107,3406868,3407021,3406136,3406673,3406786,3406107,3406868,3407021,3406136,3406673,3406786,3406115,3406988,3406136,3406673,3406786,3406115,3406988,3406136,3406673,3406115,3406988,3406144,3406673,3406988,3406144,3406673,3406988,3406144,3406673,3406988,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406673,3406673,3406673</t>
+          <t>3406136,3406019,3406242,3406019,3406668,3406253,3406136,3406019,3406242,3406019,3406668,3406325,3406136,3406019,3406242,3406019,3406668,3406325,3406136,3406091,3406242,3406091,3406668,3406645,3406136,3406091,3406466,3406091,3406668,3406645,3406136,3406091,3406466,3406091,3406868,3406693,3406136,3406099,3406466,3406099,3406868,3406693,3406136,3406099,3406466,3406099,3406868,3406709,3406136,3406107,3406786,3406107,3406868,3406709,3406136,3406107,3406786,3406107,3406868,3407021,3406136,3406107,3406786,3406107,3406868,3407021,3406136,3406115,3406786,3406115,3406988,3406136,3406115,3406786,3406115,3406988,3406136,3406115,3406115,3406988,3406144,3406673,3406988,3406144,3406673,3406988,3406144,3406673,3406988,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406144,3406673,3406673,3406673,3406673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L8 W14/25; N=116; EHP=4562.000000; air:2x3,air:11x3,air:12x2,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,heavy:80x2,medium:83x5,swarm:84x32,heavy:86x2,heavy:88x2,fast:98x5,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L8 W14/25; N=116; EHP=9388.139135; air:2x6,air:11x6,air:12x4,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:98x5,heavy:31x1,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x5,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3408136,3408673,3408242,3408019,3408668,3408253,3409022,3408136,3408673,3408242,3408019,3408668,3408253,3408136,3408673,3408242,3408019,3408668,3408325,3408136,3408673,3408242,3408091,3408668,3408325,3408136,3408673,3408242,3408091,3408668,3408645,3408136,3408673,3408466,3408091,3408668,3408645,3408136,3408673,3408466,3408099,3408868,3408693,3408136,3408673,3408466,3408099,3408868,3408693,3408136,3408673,3408466,3408099,3408868,3408709,3408136,3408673,3408466,3408107,3408868,3408709,3408136,3408673,3408786,3408107,3408868,3409021,3408136,3408673,3408786,3408107,3408868,3409021,3408136,3408673,3408786,3408115,3408988,3408136,3408673,3408786,3408115,3408988,3408144,3408673,3408115,3408988,3408144,3408673,3408988,3408144,3408673,3408988,3408144,3408673,3408988,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408673,3408673,3408673,3408673,3408673,3408673</t>
+          <t>3408136,3408019,3408242,3408019,3408668,3408253,3409022,3408136,3408019,3408242,3408019,3408668,3408253,3408136,3408019,3408242,3408019,3408668,3408325,3408136,3408091,3408242,3408091,3408668,3408325,3408136,3408091,3408242,3408091,3408668,3408645,3408136,3408091,3408466,3408091,3408668,3408645,3408136,3408099,3408466,3408099,3408868,3408693,3408136,3408099,3408466,3408099,3408868,3408693,3408136,3408099,3408466,3408099,3408868,3408709,3408136,3408107,3408466,3408107,3408868,3408709,3408136,3408107,3408786,3408107,3408868,3409021,3408136,3408107,3408786,3408107,3408868,3409021,3408136,3408115,3408786,3408115,3408988,3408136,3408115,3408786,3408115,3408988,3408144,3408115,3408115,3408988,3408144,3408673,3408988,3408144,3408673,3408988,3408144,3408673,3408988,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408144,3408673,3408673,3408673,3408673,3408673,3408673,3408673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L8 W15/25; N=122; EHP=7963.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,heavy:80x2,medium:83x6,swarm:84x34,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,elite:127x1,heavy:127x2</t>
+          <t>L8 W15/25; N=122; EHP=16384.585284; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,elite:127x1,fast:30x5,fast:58x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x14,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3410136,3410673,3410242,3410019,3410668,3410253,3410136,3410673,3410242,3410019,3410668,3410253,3410136,3410673,3410242,3410019,3410668,3410325,3410136,3410673,3410242,3410091,3410668,3410325,3410136,3410673,3410242,3410091,3410668,3410645,3410136,3410673,3410466,3410091,3410668,3410645,3410136,3410673,3410466,3410099,3410668,3410693,3410136,3410673,3410466,3410099,3410868,3410693,3410136,3410673,3410466,3410099,3410868,3410709,3410136,3410673,3410466,3410107,3410868,3410709,3410136,3410673,3410786,3410107,3410868,3411021,3410136,3410673,3410786,3410107,3410868,3411021,3410136,3410673,3410786,3410115,3410868,3410136,3410673,3410786,3410115,3410988,3410136,3410673,3410786,3410115,3410988,3410136,3410673,3410988,3410144,3410673,3410988,3410144,3410673,3410988,3410144,3410673,3410988,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410673,3410673,3410673</t>
+          <t>3410136,3410019,3410242,3410019,3410668,3410253,3410136,3410019,3410242,3410019,3410668,3410253,3410136,3410019,3410242,3410019,3410668,3410325,3410136,3410091,3410242,3410091,3410668,3410325,3410136,3410091,3410242,3410091,3410668,3410645,3410136,3410091,3410466,3410091,3410668,3410645,3410136,3410099,3410466,3410099,3410668,3410693,3410136,3410099,3410466,3410099,3410868,3410693,3410136,3410099,3410466,3410099,3410868,3410709,3410136,3410107,3410466,3410107,3410868,3410709,3410136,3410107,3410786,3410107,3410868,3411021,3410136,3410107,3410786,3410107,3410868,3411021,3410136,3410115,3410786,3410115,3410868,3410136,3410115,3410786,3410115,3410988,3410136,3410115,3410786,3410115,3410988,3410136,3410673,3410988,3410144,3410673,3410988,3410144,3410673,3410988,3410144,3410673,3410988,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410144,3410673,3410673,3410673,3410673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L8 W16/25; N=128; EHP=8123.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,heavy:80x2,medium:83x7,swarm:84x35,heavy:86x2,heavy:88x2,fast:98x5,medium:108x6,medium:123x6,heavy:127x2</t>
+          <t>L8 W16/25; N=128; EHP=16710.372316; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x5,fast:58x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x6,medium:123x6,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3412136,3412673,3412242,3412019,3412668,3412253,3412136,3412673,3412242,3412019,3412668,3412253,3412136,3412673,3412242,3412019,3412668,3412325,3412136,3412673,3412242,3412091,3412668,3412325,3412136,3412673,3412242,3412091,3412668,3412645,3412136,3412673,3412466,3412091,3412668,3412645,3412136,3412673,3412466,3412099,3412868,3412645,3412136,3412673,3412466,3412099,3412868,3412693,3412136,3412673,3412466,3412099,3412868,3412693,3412136,3412673,3412466,3412107,3412868,3412709,3412136,3412673,3412786,3412107,3412868,3412709,3412136,3412673,3412786,3412107,3412868,3413021,3412136,3412673,3412786,3412115,3412868,3413021,3412136,3412673,3412786,3412115,3412988,3412136,3412673,3412786,3412115,3412988,3412136,3412673,3412786,3412115,3412988,3412144,3412673,3412988,3412144,3412673,3412988,3412144,3412673,3412988,3412144,3412673,3412988,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412673,3412673,3412673,3412673,3412673</t>
+          <t>3412136,3412019,3412242,3412019,3412668,3412253,3412136,3412019,3412242,3412019,3412668,3412253,3412136,3412019,3412242,3412019,3412668,3412325,3412136,3412091,3412242,3412091,3412668,3412325,3412136,3412091,3412242,3412091,3412668,3412645,3412136,3412091,3412466,3412091,3412668,3412645,3412136,3412099,3412466,3412099,3412868,3412645,3412136,3412099,3412466,3412099,3412868,3412693,3412136,3412099,3412466,3412099,3412868,3412693,3412136,3412107,3412466,3412107,3412868,3412709,3412136,3412107,3412786,3412107,3412868,3412709,3412136,3412107,3412786,3412107,3412868,3413021,3412136,3412115,3412786,3412115,3412868,3413021,3412136,3412115,3412786,3412115,3412988,3412136,3412115,3412786,3412115,3412988,3412136,3412115,3412786,3412115,3412988,3412144,3412673,3412988,3412144,3412673,3412988,3412144,3412673,3412988,3412144,3412673,3412988,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412144,3412673,3412673,3412673,3412673,3412673,3412673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L8 W17/25; N=134; EHP=8286.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x4,normal:17x16,normal:18x16,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,heavy:80x3,medium:83x6,swarm:84x37,heavy:86x2,heavy:88x2,fast:98x6,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L8 W17/25; N=134; EHP=17048.913567; air:2x6,air:11x6,air:12x6,air:13x6,air:14x8,fast:30x5,fast:58x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:80x3,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x6,medium:108x7,medium:123x7,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3414136,3414673,3414242,3414019,3414668,3414253,3414136,3414673,3414242,3414019,3414668,3414253,3414136,3414673,3414242,3414019,3414668,3414253,3414136,3414673,3414242,3414019,3414668,3414325,3414136,3414673,3414242,3414091,3414668,3414325,3414136,3414673,3414466,3414091,3414668,3414645,3414136,3414673,3414466,3414091,3414668,3414645,3414136,3414673,3414466,3414099,3414868,3414693,3414136,3414673,3414466,3414099,3414868,3414693,3414136,3414673,3414466,3414099,3414868,3414693,3414136,3414673,3414466,3414099,3414868,3414709,3414136,3414673,3414786,3414107,3414868,3414709,3414136,3414673,3414786,3414107,3414868,3415021,3414136,3414673,3414786,3414107,3414868,3415021,3414136,3414673,3414786,3414115,3414988,3414136,3414673,3414786,3414115,3414988,3414144,3414673,3414115,3414988,3414144,3414673,3414988,3414144,3414673,3414988,3414144,3414673,3414988,3414144,3414673,3414988,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414673,3414673,3414673,3414673,3414673,3414673</t>
+          <t>3414136,3414019,3414242,3414019,3414668,3414253,3414136,3414019,3414242,3414019,3414668,3414253,3414136,3414019,3414242,3414019,3414668,3414253,3414136,3414019,3414242,3414019,3414668,3414325,3414136,3414091,3414242,3414091,3414668,3414325,3414136,3414091,3414466,3414091,3414668,3414645,3414136,3414091,3414466,3414091,3414668,3414645,3414136,3414099,3414466,3414099,3414868,3414693,3414136,3414099,3414466,3414099,3414868,3414693,3414136,3414099,3414466,3414099,3414868,3414693,3414136,3414099,3414466,3414099,3414868,3414709,3414136,3414107,3414786,3414107,3414868,3414709,3414136,3414107,3414786,3414107,3414868,3415021,3414136,3414107,3414786,3414107,3414868,3415021,3414136,3414115,3414786,3414115,3414988,3414136,3414115,3414786,3414115,3414988,3414144,3414115,3414115,3414988,3414144,3414673,3414988,3414144,3414673,3414988,3414144,3414673,3414988,3414144,3414673,3414988,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414144,3414673,3414673,3414673,3414673,3414673,3414673,3414673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L8 W18/25; N=140; EHP=8854.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x3,normal:17x16,normal:18x17,fast:30x5,heavy:31x3,heavy:40x2,fast:58x6,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x3,heavy:88x2,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L8 W18/25; N=140; EHP=18220.527413; air:2x8,air:11x6,air:12x8,air:13x6,air:14x6,fast:30x5,fast:58x6,fast:98x5,heavy:31x3,heavy:40x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x16,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3416136,3416673,3416242,3416019,3416668,3416253,3416136,3416673,3416242,3416019,3416668,3416253,3416136,3416673,3416242,3416019,3416668,3416253,3416136,3416673,3416242,3416019,3416668,3416325,3416136,3416673,3416242,3416091,3416668,3416325,3416136,3416673,3416242,3416091,3416668,3416325,3416136,3416673,3416466,3416091,3416668,3416645,3416136,3416673,3416466,3416091,3416868,3416645,3416136,3416673,3416466,3416099,3416868,3416693,3416136,3416673,3416466,3416099,3416868,3416693,3416136,3416673,3416466,3416099,3416868,3416709,3416136,3416673,3416786,3416107,3416868,3416709,3416136,3416673,3416786,3416107,3416868,3417021,3416136,3416673,3416786,3416107,3416868,3417021,3416136,3416673,3416786,3416107,3416988,3416136,3416673,3416786,3416115,3416988,3416136,3416673,3416786,3416115,3416988,3416136,3416673,3416115,3416988,3416144,3416673,3416988,3416144,3416673,3416988,3416144,3416673,3416988,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416673,3416673,3416673,3416673</t>
+          <t>3416136,3416019,3416242,3416019,3416668,3416253,3416136,3416019,3416242,3416019,3416668,3416253,3416136,3416019,3416242,3416019,3416668,3416253,3416136,3416019,3416242,3416019,3416668,3416325,3416136,3416091,3416242,3416091,3416668,3416325,3416136,3416091,3416242,3416091,3416668,3416325,3416136,3416091,3416466,3416091,3416668,3416645,3416136,3416091,3416466,3416091,3416868,3416645,3416136,3416099,3416466,3416099,3416868,3416693,3416136,3416099,3416466,3416099,3416868,3416693,3416136,3416099,3416466,3416099,3416868,3416709,3416136,3416107,3416786,3416107,3416868,3416709,3416136,3416107,3416786,3416107,3416868,3417021,3416136,3416107,3416786,3416107,3416868,3417021,3416136,3416107,3416786,3416107,3416988,3416136,3416115,3416786,3416115,3416988,3416136,3416115,3416786,3416115,3416988,3416136,3416115,3416115,3416988,3416144,3416673,3416988,3416144,3416673,3416988,3416144,3416673,3416988,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416144,3416673,3416673,3416673,3416673,3416673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L8 W19/25; N=146; EHP=10254.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x3,normal:17x18,normal:18x18,fast:30x6,heavy:31x3,heavy:40x3,fast:58x5,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x6,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L8 W19/25; N=146; EHP=21107.424025; air:2x8,air:11x8,air:12x6,air:13x8,air:14x6,fast:30x6,fast:58x5,fast:98x6,heavy:31x3,heavy:40x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3418136,3418673,3418242,3418019,3418668,3418253,3419022,3418136,3418673,3418242,3418019,3418668,3418253,3418136,3418673,3418242,3418019,3418668,3418325,3418136,3418673,3418242,3418091,3418668,3418325,3418136,3418673,3418242,3418091,3418668,3418325,3418136,3418673,3418242,3418091,3418668,3418645,3418136,3418673,3418466,3418091,3418668,3418645,3418136,3418673,3418466,3418099,3418868,3418693,3418136,3418673,3418466,3418099,3418868,3418693,3418136,3418673,3418466,3418099,3418868,3418709,3418136,3418673,3418466,3418107,3418868,3418709,3418136,3418673,3418466,3418107,3418868,3418709,3418136,3418673,3418786,3418107,3418868,3419021,3418136,3418673,3418786,3418107,3418868,3419021,3418136,3418673,3418786,3418115,3418988,3419021,3418136,3418673,3418786,3418115,3418988,3418136,3418673,3418786,3418115,3418988,3418136,3418673,3418786,3418115,3418988,3418144,3418673,3418988,3418144,3418673,3418988,3418144,3418673,3418988,3418144,3418673,3418988,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418673,3418673,3418673,3418673,3418673,3418673</t>
+          <t>3418136,3418019,3418242,3418019,3418668,3418253,3419022,3418136,3418019,3418242,3418019,3418668,3418253,3418136,3418019,3418242,3418019,3418668,3418325,3418136,3418091,3418242,3418091,3418668,3418325,3418136,3418091,3418242,3418091,3418668,3418325,3418136,3418091,3418242,3418091,3418668,3418645,3418136,3418091,3418466,3418091,3418668,3418645,3418136,3418099,3418466,3418099,3418868,3418693,3418136,3418099,3418466,3418099,3418868,3418693,3418136,3418099,3418466,3418099,3418868,3418709,3418136,3418107,3418466,3418107,3418868,3418709,3418136,3418107,3418466,3418107,3418868,3418709,3418136,3418107,3418786,3418107,3418868,3419021,3418136,3418107,3418786,3418107,3418868,3419021,3418136,3418115,3418786,3418115,3418988,3419021,3418136,3418115,3418786,3418115,3418988,3418136,3418115,3418786,3418115,3418988,3418136,3418115,3418786,3418115,3418988,3418144,3418673,3418988,3418144,3418673,3418988,3418144,3418673,3418988,3418144,3418673,3418988,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418144,3418673,3418673,3418673,3418673,3418673,3418673,3418673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L8 W20/25; N=152; EHP=17221.000000; air:2x3,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x18,normal:18x18,fast:30x6,heavy:31x2,heavy:40x3,fast:58x6,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x3,fast:98x6,medium:108x7,medium:123x8,elite:127x1,heavy:127x3</t>
+          <t>L8 W20/25; N=152; EHP=35420.721688; air:2x6,air:11x8,air:12x6,air:13x8,air:14x8,elite:127x1,fast:30x6,fast:58x6,fast:98x6,heavy:31x2,heavy:40x3,heavy:80x2,heavy:86x2,heavy:88x3,heavy:127x3,medium:83x7,medium:108x7,medium:123x8,normal:17x18,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10017219,10017227,10017221,10048540,10017226,10017222,10017219,10017227,10017221,10048540,10017226,10017222,10017219,10017227,10017221,10048540,10017226,10017223,10017219,10017227,10017221,10048540,10017226,10017223,10017219,10017227,10017221,10017216,10017226,10017225,10017219,10017227,10017221,10017216,10017226,10017225,10017219,10017227,10017224,10017216,10017226,10017225,10017219,10017227,10017224,10017216,10017226,10017228,10017219,10017227,10017224,10048541,10017231,10017228,10017219,10017227,10017224,10048541,10017231,10017229,10017219,10017227,10017224,10048541,10017231,10017229,10017219,10017227,10017224,10048541,10017231,10017229,10017219,10017227,10017230,10017217,10017231,10017233,10017219,10017227,10017230,10017217,10017231,10017233,10017219,10017227,10017230,10017217,10017231,10017233,10017219,10017227,10017230,10017218,10017231,10017219,10017227,10017230,10017218,10017232,10017219,10017227,10017230,10017218,10017232,10017219,10017227,10017218,10017232,10017219,10017227,10017232,10017220,10017227,10017232,10017220,10017227,10017232,10017220,10017227,10017232,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017227,10017227,10017227,10017227,10017227</t>
+          <t>10017219,10048540,10017221,10048540,10017226,10017222,10017219,10048540,10017221,10048540,10017226,10017222,10017219,10048540,10017221,10048540,10017226,10017223,10017219,10048540,10017221,10048540,10017226,10017223,10017219,10017216,10017221,10017216,10017226,10017225,10017219,10017216,10017221,10017216,10017226,10017225,10017219,10017216,10017224,10017216,10017226,10017225,10017219,10017216,10017224,10017216,10017226,10017228,10017219,10048541,10017224,10048541,10017231,10017228,10017219,10048541,10017224,10048541,10017231,10017229,10017219,10048541,10017224,10048541,10017231,10017229,10017219,10048541,10017224,10048541,10017231,10017229,10017219,10017217,10017230,10017217,10017231,10017233,10017219,10017217,10017230,10017217,10017231,10017233,10017219,10017217,10017230,10017217,10017231,10017233,10017219,10017218,10017230,10017218,10017231,10017219,10017218,10017230,10017218,10017232,10017219,10017218,10017230,10017218,10017232,10017219,10017218,10017218,10017232,10017219,10017227,10017232,10017220,10017227,10017232,10017220,10017227,10017232,10017220,10017227,10017232,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017220,10017227,10017227,10017227,10017227,10017227,10017227</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L8 W21/25; N=158; EHP=17566.000000; air:2x4,air:11x4,air:12x4,air:13x3,air:14x4,normal:17x20,normal:18x19,fast:30x6,heavy:31x2,heavy:40x2,fast:58x6,heavy:80x3,medium:83x8,swarm:84x44,heavy:86x2,heavy:88x3,fast:98x6,medium:108x8,medium:123x7,heavy:127x3</t>
+          <t>L8 W21/25; N=158; EHP=36148.169466; air:2x8,air:11x8,air:12x8,air:13x6,air:14x8,fast:30x6,fast:58x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:80x3,heavy:86x2,heavy:88x3,heavy:127x3,medium:83x8,medium:108x8,medium:123x7,normal:17x20,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10017237,10017245,10017239,10048542,10017244,10017240,10017237,10017245,10017239,10048542,10017244,10017240,10017237,10017245,10017239,10048542,10017244,10017240,10017237,10017245,10017239,10048542,10017244,10017241,10017237,10017245,10017239,10017234,10017244,10017241,10017237,10017245,10017239,10017234,10017244,10017243,10017237,10017245,10017239,10017234,10017244,10017243,10017237,10017245,10017242,10017234,10017244,10017243,10017237,10017245,10017242,10048543,10017249,10017246,10017237,10017245,10017242,10048543,10017249,10017246,10017237,10017245,10017242,10048543,10017249,10017246,10017237,10017245,10017242,10048543,10017249,10017247,10017237,10017245,10017242,10017235,10017249,10017247,10017237,10017245,10017248,10017235,10017249,10017247,10017237,10017245,10017248,10017235,10017249,10017251,10017237,10017245,10017248,10017235,10017249,10017251,10017237,10017245,10017248,10017236,10017250,10017237,10017245,10017248,10017236,10017250,10017237,10017245,10017248,10017236,10017250,10017237,10017245,10017236,10017250,10017238,10017245,10017250,10017238,10017245,10017250,10017238,10017245,10017250,10017238,10017245,10017250,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017245,10017245,10017245,10017245,10017245</t>
+          <t>10017237,10048542,10017239,10048542,10017244,10017240,10017237,10048542,10017239,10048542,10017244,10017240,10017237,10048542,10017239,10048542,10017244,10017240,10017237,10048542,10017239,10048542,10017244,10017241,10017237,10017234,10017239,10017234,10017244,10017241,10017237,10017234,10017239,10017234,10017244,10017243,10017237,10017234,10017239,10017234,10017244,10017243,10017237,10017234,10017242,10017234,10017244,10017243,10017237,10048543,10017242,10048543,10017249,10017246,10017237,10048543,10017242,10048543,10017249,10017246,10017237,10048543,10017242,10048543,10017249,10017246,10017237,10048543,10017242,10048543,10017249,10017247,10017237,10017235,10017242,10017235,10017249,10017247,10017237,10017235,10017248,10017235,10017249,10017247,10017237,10017235,10017248,10017235,10017249,10017251,10017237,10017235,10017248,10017235,10017249,10017251,10017237,10017236,10017248,10017236,10017250,10017237,10017236,10017248,10017236,10017250,10017237,10017236,10017248,10017236,10017250,10017237,10017236,10017236,10017250,10017238,10017245,10017250,10017238,10017245,10017250,10017238,10017245,10017250,10017238,10017245,10017250,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017238,10017245,10017245,10017245,10017245,10017245,10017245</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L8 W22/25; N=164; EHP=17918.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x20,fast:30x7,heavy:31x3,heavy:40x2,fast:58x6,heavy:80x3,medium:83x8,swarm:84x45,heavy:86x3,heavy:88x3,fast:98x6,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L8 W22/25; N=164; EHP=36876.900499; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x7,fast:58x6,fast:98x6,heavy:31x3,heavy:40x2,heavy:80x3,heavy:86x3,heavy:88x3,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x20,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10017255,10017263,10017257,10048544,10017262,10017258,10017255,10017263,10017257,10048544,10017262,10017258,10017255,10017263,10017257,10048544,10017262,10017258,10017255,10017263,10017257,10048544,10017262,10017259,10017255,10017263,10017257,10017252,10017262,10017259,10017255,10017263,10017257,10017252,10017262,10017259,10017255,10017263,10017260,10017252,10017262,10017261,10017255,10017263,10017260,10017252,10017262,10017261,10017255,10017263,10017260,10048545,10017267,10017261,10017255,10017263,10017260,10048545,10017267,10017264,10017255,10017263,10017260,10048545,10017267,10017264,10017255,10017263,10017260,10048545,10017267,10017264,10017255,10017263,10017260,10017253,10017267,10017265,10017255,10017263,10017266,10017253,10017267,10017265,10017255,10017263,10017266,10017253,10017267,10017269,10017255,10017263,10017266,10017253,10017267,10017269,10017255,10017263,10017266,10017254,10017268,10017269,10017255,10017263,10017266,10017254,10017268,10017255,10017263,10017266,10017254,10017268,10017255,10017263,10017266,10017254,10017268,10017255,10017263,10017268,10017256,10017263,10017268,10017256,10017263,10017268,10017256,10017263,10017268,10017256,10017263,10017268,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017263,10017263,10017263,10017263,10017263,10017263</t>
+          <t>10017255,10048544,10017257,10048544,10017262,10017258,10017255,10048544,10017257,10048544,10017262,10017258,10017255,10048544,10017257,10048544,10017262,10017258,10017255,10048544,10017257,10048544,10017262,10017259,10017255,10017252,10017257,10017252,10017262,10017259,10017255,10017252,10017257,10017252,10017262,10017259,10017255,10017252,10017260,10017252,10017262,10017261,10017255,10017252,10017260,10017252,10017262,10017261,10017255,10048545,10017260,10048545,10017267,10017261,10017255,10048545,10017260,10048545,10017267,10017264,10017255,10048545,10017260,10048545,10017267,10017264,10017255,10048545,10017260,10048545,10017267,10017264,10017255,10017253,10017260,10017253,10017267,10017265,10017255,10017253,10017266,10017253,10017267,10017265,10017255,10017253,10017266,10017253,10017267,10017269,10017255,10017253,10017266,10017253,10017267,10017269,10017255,10017254,10017266,10017254,10017268,10017269,10017255,10017254,10017266,10017254,10017268,10017255,10017254,10017266,10017254,10017268,10017255,10017254,10017266,10017254,10017268,10017255,10017263,10017268,10017256,10017263,10017268,10017256,10017263,10017268,10017256,10017263,10017268,10017256,10017263,10017268,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017256,10017263,10017263,10017263,10017263,10017263,10017263,10017263</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L8 W23/25; N=170; EHP=18277.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x6,heavy:31x3,heavy:40x3,fast:58x7,heavy:80x3,medium:83x8,swarm:84x47,heavy:86x3,heavy:88x2,fast:98x7,medium:108x8,medium:123x9,heavy:127x3</t>
+          <t>L8 W23/25; N=170; EHP=37598.418621; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x6,fast:58x7,fast:98x7,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x2,heavy:127x3,medium:83x8,medium:108x8,medium:123x9,normal:17x21,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10017273,10017281,10017275,10048546,10017280,10017276,10017273,10017281,10017275,10048546,10017280,10017276,10017273,10017281,10017275,10048546,10017280,10017276,10017273,10017281,10017275,10048546,10017280,10017277,10017273,10017281,10017275,10048546,10017280,10017277,10017273,10017281,10017275,10017270,10017280,10017277,10017273,10017281,10017275,10017270,10017280,10017279,10017273,10017281,10017278,10017270,10017280,10017279,10017273,10017281,10017278,10017270,10017280,10017282,10017273,10017281,10017278,10048547,10017285,10017282,10017273,10017281,10017278,10048547,10017285,10017282,10017273,10017281,10017278,10048547,10017285,10017283,10017273,10017281,10017278,10048547,10017285,10017283,10017273,10017281,10017278,10017271,10017285,10017283,10017273,10017281,10017284,10017271,10017285,10017287,10017273,10017281,10017284,10017271,10017285,10017287,10017273,10017281,10017284,10017271,10017285,10017287,10017273,10017281,10017284,10017272,10017285,10017273,10017281,10017284,10017272,10017286,10017273,10017281,10017284,10017272,10017286,10017273,10017281,10017284,10017272,10017286,10017274,10017281,10017286,10017274,10017281,10017286,10017274,10017281,10017286,10017274,10017281,10017286,10017274,10017281,10017286,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017281,10017281,10017281,10017281,10017281,10017281,10017281</t>
+          <t>10017273,10048546,10017275,10048546,10017280,10017276,10017273,10048546,10017275,10048546,10017280,10017276,10017273,10048546,10017275,10048546,10017280,10017276,10017273,10048546,10017275,10048546,10017280,10017277,10017273,10048546,10017275,10048546,10017280,10017277,10017273,10017270,10017275,10017270,10017280,10017277,10017273,10017270,10017275,10017270,10017280,10017279,10017273,10017270,10017278,10017270,10017280,10017279,10017273,10017270,10017278,10017270,10017280,10017282,10017273,10048547,10017278,10048547,10017285,10017282,10017273,10048547,10017278,10048547,10017285,10017282,10017273,10048547,10017278,10048547,10017285,10017283,10017273,10048547,10017278,10048547,10017285,10017283,10017273,10017271,10017278,10017271,10017285,10017283,10017273,10017271,10017284,10017271,10017285,10017287,10017273,10017271,10017284,10017271,10017285,10017287,10017273,10017271,10017284,10017271,10017285,10017287,10017273,10017272,10017284,10017272,10017285,10017273,10017272,10017284,10017272,10017286,10017273,10017272,10017284,10017272,10017286,10017273,10017272,10017284,10017272,10017286,10017274,10017281,10017286,10017274,10017281,10017286,10017274,10017281,10017286,10017274,10017281,10017286,10017274,10017281,10017286,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017274,10017281,10017281,10017281,10017281,10017281,10017281,10017281,10017281</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L8 W24/25; N=176; EHP=19570.000000; air:2x5,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x21,fast:30x7,heavy:31x3,heavy:40x3,fast:58x7,heavy:80x2,medium:83x9,swarm:84x49,heavy:86x3,heavy:88x3,fast:98x7,medium:108x9,medium:123x8,heavy:127x3</t>
+          <t>L8 W24/25; N=176; EHP=40267.076809; air:2x10,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x7,fast:58x7,fast:98x7,heavy:31x3,heavy:40x3,heavy:80x2,heavy:86x3,heavy:88x3,heavy:127x3,medium:83x9,medium:108x9,medium:123x8,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10017291,10017299,10017293,10048548,10017298,10017294,10017304,10017291,10017299,10017293,10048548,10017298,10017294,10017291,10017299,10017293,10048548,10017298,10017294,10017291,10017299,10017293,10048548,10017298,10017295,10017291,10017299,10017293,10017288,10017298,10017295,10017291,10017299,10017293,10017288,10017298,10017295,10017291,10017299,10017293,10017288,10017298,10017297,10017291,10017299,10017296,10017288,10017298,10017297,10017291,10017299,10017296,10017288,10017298,10017297,10017291,10017299,10017296,10048549,10017303,10017300,10017291,10017299,10017296,10048549,10017303,10017300,10017291,10017299,10017296,10048549,10017303,10017300,10017291,10017299,10017296,10048549,10017303,10017301,10017291,10017299,10017296,10017289,10017303,10017301,10017291,10017299,10017302,10017289,10017303,10017301,10017291,10017299,10017302,10017289,10017303,10017306,10017291,10017299,10017302,10017289,10017303,10017306,10017291,10017299,10017302,10017289,10017303,10017306,10017291,10017299,10017302,10017290,10017305,10017291,10017299,10017302,10017290,10017305,10017291,10017299,10017302,10017290,10017305,10017291,10017299,10017290,10017305,10017292,10017299,10017305,10017292,10017299,10017305,10017292,10017299,10017305,10017292,10017299,10017305,10017292,10017299,10017305,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017299,10017299,10017299,10017299,10017299,10017299,10017299</t>
+          <t>10017291,10048548,10017293,10048548,10017298,10017294,10017304,10017291,10048548,10017293,10048548,10017298,10017294,10017291,10048548,10017293,10048548,10017298,10017294,10017291,10048548,10017293,10048548,10017298,10017295,10017291,10017288,10017293,10017288,10017298,10017295,10017291,10017288,10017293,10017288,10017298,10017295,10017291,10017288,10017293,10017288,10017298,10017297,10017291,10017288,10017296,10017288,10017298,10017297,10017291,10017288,10017296,10017288,10017298,10017297,10017291,10048549,10017296,10048549,10017303,10017300,10017291,10048549,10017296,10048549,10017303,10017300,10017291,10048549,10017296,10048549,10017303,10017300,10017291,10048549,10017296,10048549,10017303,10017301,10017291,10017289,10017296,10017289,10017303,10017301,10017291,10017289,10017302,10017289,10017303,10017301,10017291,10017289,10017302,10017289,10017303,10017306,10017291,10017289,10017302,10017289,10017303,10017306,10017291,10017289,10017302,10017289,10017303,10017306,10017291,10017290,10017302,10017290,10017305,10017291,10017290,10017302,10017290,10017305,10017291,10017290,10017302,10017290,10017305,10017291,10017290,10017290,10017305,10017292,10017299,10017305,10017292,10017299,10017305,10017292,10017299,10017305,10017292,10017299,10017305,10017292,10017299,10017305,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017292,10017299,10017299,10017299,10017299,10017299,10017299,10017299,10017299</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L8 W25/25; N=182; EHP=39066.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x21,fast:30x7,heavy:31x3,heavy:40x3,fast:58x7,heavy:80x3,medium:83x9,swarm:84x50,heavy:86x3,heavy:88x3,fast:98x7,medium:108x9,elite:123x1,medium:123x9,heavy:127x3</t>
+          <t>L8 W25/25; N=182; EHP=80371.995080; air:2x8,air:11x10,air:12x8,air:13x10,air:14x8,elite:123x1,fast:30x7,fast:58x7,fast:98x7,heavy:31x3,heavy:40x3,heavy:80x3,heavy:86x3,heavy:88x3,heavy:127x3,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L08/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L08/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>266</v>
+        <v>320</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>245</v>
+        <v>330</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>231</v>
+        <v>260</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>224</v>
+        <v>300</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>210</v>
+        <v>290</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>203</v>
+        <v>340</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>196</v>
+        <v>250</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>189</v>
+        <v>280</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>161</v>
+        <v>260</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>154</v>
+        <v>330</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>140</v>
+        <v>270</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>250</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>340</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
